--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6985,0.1472,0.1017,0.0870</t>
-  </si>
-  <si>
-    <t>0.0228,0.0014,0.0003,0.9938</t>
-  </si>
-  <si>
-    <t>0.6439,0.0222,0.0027,0.3635</t>
-  </si>
-  <si>
-    <t>0.1139,0.0146,0.0160,0.9412</t>
-  </si>
-  <si>
-    <t>0.9955,0.0012,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9918,0.0020,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9916,0.0036,0.0014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9962,0.0005,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9929,0.0021,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9931,0.0035,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9943,0.0011,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9941,0.0021,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.4944,0.1231,0.4096,0.0604</t>
-  </si>
-  <si>
-    <t>0.4622,0.0611,0.5525,0.0128</t>
-  </si>
-  <si>
-    <t>0.1328,0.1051,0.7845,0.0026</t>
-  </si>
-  <si>
-    <t>0.2137,0.0550,0.8016,0.0128</t>
-  </si>
-  <si>
-    <t>0.4862,0.0315,0.6387,0.0090</t>
-  </si>
-  <si>
-    <t>0.0047,0.9894,0.0143,0.0006</t>
-  </si>
-  <si>
-    <t>0.0213,0.9743,0.0084,0.0003</t>
-  </si>
-  <si>
-    <t>0.1142,0.9156,0.0052,0.0012</t>
-  </si>
-  <si>
-    <t>0.0134,0.9769,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.0019,0.9945,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.3087,0.0149,0.4530,0.3084</t>
-  </si>
-  <si>
-    <t>0.4149,0.0205,0.6392,0.0300</t>
-  </si>
-  <si>
-    <t>0.0280,0.0628,0.9245,0.0396</t>
-  </si>
-  <si>
-    <t>0.1082,0.0101,0.9133,0.0146</t>
-  </si>
-  <si>
-    <t>0.0237,0.0047,0.9704,0.0179</t>
-  </si>
-  <si>
-    <t>0.1812,0.0115,0.7784,0.0834</t>
-  </si>
-  <si>
-    <t>0.0029,0.0016,0.9962,0.0011</t>
-  </si>
-  <si>
-    <t>0.5152,0.6199,0.0117,0.0017</t>
-  </si>
-  <si>
-    <t>0.5998,0.0561,0.4578,0.0298</t>
-  </si>
-  <si>
-    <t>0.0011,0.0109,0.9963,0.0018</t>
-  </si>
-  <si>
-    <t>0.0125,0.8935,0.3449,0.0003</t>
-  </si>
-  <si>
-    <t>0.9113,0.0640,0.0059,0.0133</t>
-  </si>
-  <si>
-    <t>0.6758,0.2746,0.0788,0.0027</t>
-  </si>
-  <si>
-    <t>0.8855,0.1192,0.0185,0.0070</t>
-  </si>
-  <si>
-    <t>0.0139,0.9634,0.2361,0.0011</t>
-  </si>
-  <si>
-    <t>0.0321,0.6505,0.4600,0.0518</t>
-  </si>
-  <si>
-    <t>0.0198,0.0438,0.9415,0.0147</t>
-  </si>
-  <si>
-    <t>0.0666,0.2337,0.7851,0.0295</t>
-  </si>
-  <si>
-    <t>0.4628,0.0134,0.6144,0.0163</t>
-  </si>
-  <si>
-    <t>0.0320,0.2464,0.8921,0.0022</t>
-  </si>
-  <si>
-    <t>0.0278,0.8245,0.2184,0.0015</t>
-  </si>
-  <si>
-    <t>0.0146,0.3014,0.9227,0.0020</t>
-  </si>
-  <si>
-    <t>0.0147,0.9176,0.0131,0.4269</t>
-  </si>
-  <si>
-    <t>0.0016,0.9887,0.0447,0.0038</t>
-  </si>
-  <si>
-    <t>0.0003,0.9943,0.0501,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.0107,0.0020</t>
-  </si>
-  <si>
-    <t>0.0013,0.0543,0.9758,0.0086</t>
-  </si>
-  <si>
-    <t>0.0050,0.5610,0.9511,0.0003</t>
-  </si>
-  <si>
-    <t>0.0602,0.0172,0.9126,0.0486</t>
-  </si>
-  <si>
-    <t>0.0142,0.0160,0.9771,0.0014</t>
-  </si>
-  <si>
-    <t>0.0012,0.0063,0.9947,0.0037</t>
-  </si>
-  <si>
-    <t>0.0049,0.0041,0.9919,0.0006</t>
-  </si>
-  <si>
-    <t>0.9617,0.0537,0.0073,0.0007</t>
-  </si>
-  <si>
-    <t>0.9700,0.0069,0.0015,0.0122</t>
-  </si>
-  <si>
-    <t>0.9562,0.0349,0.0045,0.0075</t>
-  </si>
-  <si>
-    <t>0.0079,0.0618,0.9760,0.0086</t>
-  </si>
-  <si>
-    <t>0.9860,0.0105,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9893,0.0138,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9836,0.0114,0.0018,0.0022</t>
-  </si>
-  <si>
-    <t>0.0006,0.8719,0.9585,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0077,0.9933,0.0047</t>
-  </si>
-  <si>
-    <t>0.0134,0.4872,0.8628,0.0094</t>
-  </si>
-  <si>
-    <t>0.0003,0.9070,0.9780,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0187,0.9932,0.0026</t>
-  </si>
-  <si>
-    <t>0.0118,0.9671,0.0185,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.9850,0.0089,0.0003</t>
-  </si>
-  <si>
-    <t>0.6825,0.0964,0.3646,0.0021</t>
-  </si>
-  <si>
-    <t>0.1246,0.3665,0.7143,0.0011</t>
-  </si>
-  <si>
-    <t>0.0116,0.0475,0.9605,0.0302</t>
-  </si>
-  <si>
-    <t>0.0010,0.8918,0.8701,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9532,0.6701,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9871,0.2232,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9873,0.8198,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0005,0.0193,0.9952</t>
-  </si>
-  <si>
-    <t>0.0031,0.0107,0.0001,0.9973</t>
-  </si>
-  <si>
-    <t>0.0335,0.0085,0.0083,0.9795</t>
-  </si>
-  <si>
-    <t>0.0049,0.0006,0.0225,0.9883</t>
-  </si>
-  <si>
-    <t>0.0204,0.0132,0.0080,0.9839</t>
-  </si>
-  <si>
-    <t>0.0075,0.0013,0.0009,0.9965</t>
-  </si>
-  <si>
-    <t>0.0005,0.9448,0.9540,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.1271,0.9811,0.0020</t>
-  </si>
-  <si>
-    <t>0.0461,0.4777,0.6336,0.0148</t>
-  </si>
-  <si>
-    <t>0.0044,0.8144,0.8046,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.9405,0.9012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.6848,0.8445,0.0001</t>
-  </si>
-  <si>
-    <t>0.9906,0.0067,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9948,0.0046,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9839,0.0247,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9943,0.0010,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9779,0.0249,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9788,0.0363,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9915,0.0062,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9915,0.0026,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.9881,0.0041,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9961,0.0046,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0030,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9969,0.0019,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0009,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.9948,0.0037,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0016,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9958,0.0032,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9977,0.0025</t>
-  </si>
-  <si>
-    <t>0.0404,0.0244,0.9379,0.0111</t>
-  </si>
-  <si>
-    <t>0.7137,0.0285,0.1555,0.0604</t>
-  </si>
-  <si>
-    <t>0.0271,0.0156,0.9539,0.0054</t>
-  </si>
-  <si>
-    <t>0.0245,0.9664,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.0071,0.9854,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.1211,0.8744,0.0065,0.0137</t>
-  </si>
-  <si>
-    <t>0.0389,0.9519,0.0061,0.0011</t>
-  </si>
-  <si>
-    <t>0.0128,0.9709,0.0059,0.0063</t>
-  </si>
-  <si>
-    <t>0.0067,0.9828,0.0024,0.0013</t>
-  </si>
-  <si>
-    <t>0.2114,0.8429,0.0080,0.0023</t>
-  </si>
-  <si>
-    <t>0.6016,0.2874,0.1283,0.0382</t>
-  </si>
-  <si>
-    <t>0.3264,0.0173,0.7772,0.0227</t>
-  </si>
-  <si>
-    <t>0.4669,0.0304,0.1400,0.3808</t>
-  </si>
-  <si>
-    <t>0.5867,0.1035,0.3875,0.0057</t>
-  </si>
-  <si>
-    <t>0.0751,0.1030,0.0727,0.8967</t>
-  </si>
-  <si>
-    <t>0.0008,0.9931,0.0213,0.0024</t>
-  </si>
-  <si>
-    <t>0.0003,0.9979,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.0410,0.8286,0.0396,0.2702</t>
-  </si>
-  <si>
-    <t>0.0001,0.9575,0.9483,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.9836,0.0235,0.0006</t>
-  </si>
-  <si>
-    <t>0.4053,0.4470,0.2300,0.0015</t>
-  </si>
-  <si>
-    <t>0.8770,0.1742,0.0225,0.0013</t>
-  </si>
-  <si>
-    <t>0.9732,0.0278,0.0021,0.0020</t>
-  </si>
-  <si>
-    <t>0.9777,0.0020,0.0005,0.0233</t>
-  </si>
-  <si>
-    <t>0.9775,0.0030,0.0001,0.0128</t>
-  </si>
-  <si>
-    <t>0.9863,0.0045,0.0008,0.0035</t>
-  </si>
-  <si>
-    <t>0.9927,0.0017,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9192,0.1196,0.0050,0.0015</t>
-  </si>
-  <si>
-    <t>0.9848,0.0058,0.0006,0.0035</t>
-  </si>
-  <si>
-    <t>0.9790,0.0083,0.0023,0.0060</t>
-  </si>
-  <si>
-    <t>0.0013,0.8890,0.9351,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.8579,0.6942,0.0002</t>
-  </si>
-  <si>
-    <t>0.0141,0.0769,0.9417,0.0131</t>
-  </si>
-  <si>
-    <t>0.0376,0.1464,0.8578,0.0023</t>
-  </si>
-  <si>
-    <t>0.7258,0.0370,0.1430,0.0616</t>
-  </si>
-  <si>
-    <t>0.7034,0.0746,0.2638,0.0148</t>
-  </si>
-  <si>
-    <t>0.3849,0.0078,0.7980,0.0082</t>
-  </si>
-  <si>
-    <t>0.4156,0.4194,0.1591,0.0599</t>
-  </si>
-  <si>
-    <t>0.0603,0.0049,0.0019,0.9810</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0014,0.0033,0.0003,0.9985</t>
-  </si>
-  <si>
-    <t>0.0107,0.0022,0.0010,0.9953</t>
-  </si>
-  <si>
-    <t>0.0025,0.8252,0.8784,0.0014</t>
-  </si>
-  <si>
-    <t>0.9808,0.0076,0.0019,0.0054</t>
-  </si>
-  <si>
-    <t>0.8317,0.2917,0.0074,0.0008</t>
-  </si>
-  <si>
-    <t>0.9878,0.0031,0.0002,0.0042</t>
-  </si>
-  <si>
-    <t>0.5926,0.5470,0.0104,0.0023</t>
-  </si>
-  <si>
-    <t>0.9711,0.0125,0.0131,0.0019</t>
-  </si>
-  <si>
-    <t>0.4655,0.0127,0.0369,0.5715</t>
-  </si>
-  <si>
-    <t>0.9730,0.0130,0.0028,0.0069</t>
-  </si>
-  <si>
-    <t>0.0002,0.1982,0.9796,0.0044</t>
-  </si>
-  <si>
-    <t>0.7676,0.0015,0.0094,0.2662</t>
-  </si>
-  <si>
-    <t>0.8921,0.0140,0.0123,0.0889</t>
-  </si>
-  <si>
-    <t>0.7116,0.2396,0.1050,0.0070</t>
-  </si>
-  <si>
-    <t>0.6855,0.2671,0.0130,0.0455</t>
-  </si>
-  <si>
-    <t>0.8956,0.1232,0.0154,0.0019</t>
-  </si>
-  <si>
-    <t>0.0596,0.9118,0.0029,0.0257</t>
-  </si>
-  <si>
-    <t>0.7767,0.2440,0.0347,0.0031</t>
-  </si>
-  <si>
-    <t>0.7616,0.2963,0.0203,0.0032</t>
-  </si>
-  <si>
-    <t>0.9811,0.0137,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.9860,0.0087,0.0005,0.0025</t>
-  </si>
-  <si>
-    <t>0.9830,0.0048,0.0022,0.0055</t>
-  </si>
-  <si>
-    <t>0.9840,0.0008,0.0013,0.0121</t>
-  </si>
-  <si>
-    <t>0.9867,0.0040,0.0002,0.0039</t>
-  </si>
-  <si>
-    <t>0.9819,0.0029,0.0004,0.0088</t>
-  </si>
-  <si>
-    <t>0.9926,0.0004,0.0001,0.0066</t>
-  </si>
-  <si>
-    <t>0.9903,0.0013,0.0001,0.0050</t>
-  </si>
-  <si>
-    <t>0.6074,0.5470,0.0226,0.0045</t>
-  </si>
-  <si>
-    <t>0.4939,0.6113,0.0212,0.0068</t>
-  </si>
-  <si>
-    <t>0.4814,0.6184,0.0261,0.0012</t>
-  </si>
-  <si>
-    <t>0.2981,0.0610,0.7973,0.0148</t>
-  </si>
-  <si>
-    <t>0.9716,0.0608,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9619,0.0438,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0067,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9757,0.0100,0.0068,0.0029</t>
-  </si>
-  <si>
-    <t>0.0035,0.0079,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.8573,0.2199,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0088,0.9946,0.0013</t>
-  </si>
-  <si>
-    <t>0.0122,0.3091,0.9493,0.0039</t>
-  </si>
-  <si>
-    <t>0.0116,0.0054,0.9829,0.0076</t>
-  </si>
-  <si>
-    <t>0.0011,0.4006,0.9792,0.0008</t>
-  </si>
-  <si>
-    <t>0.0521,0.0327,0.9423,0.0060</t>
-  </si>
-  <si>
-    <t>0.0077,0.0131,0.9862,0.0025</t>
-  </si>
-  <si>
-    <t>0.0156,0.0383,0.9751,0.0002</t>
-  </si>
-  <si>
-    <t>0.1793,0.7153,0.1053,0.0558</t>
-  </si>
-  <si>
-    <t>0.5298,0.0243,0.6499,0.0029</t>
-  </si>
-  <si>
-    <t>0.5453,0.0389,0.5319,0.0313</t>
-  </si>
-  <si>
-    <t>0.1193,0.7951,0.0987,0.0027</t>
-  </si>
-  <si>
-    <t>0.3521,0.2404,0.4943,0.0160</t>
-  </si>
-  <si>
-    <t>0.5442,0.0920,0.3747,0.0700</t>
-  </si>
-  <si>
-    <t>0.7931,0.0553,0.0845,0.0185</t>
-  </si>
-  <si>
-    <t>0.6234,0.1012,0.3966,0.0087</t>
-  </si>
-  <si>
-    <t>0.8904,0.1641,0.0115,0.0029</t>
-  </si>
-  <si>
-    <t>0.9211,0.1593,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.9241,0.1448,0.0035,0.0013</t>
-  </si>
-  <si>
-    <t>0.9864,0.0121,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.8479,0.2234,0.0092,0.0031</t>
-  </si>
-  <si>
-    <t>0.6682,0.0728,0.1026,0.1149</t>
-  </si>
-  <si>
-    <t>0.7341,0.0259,0.3322,0.0106</t>
-  </si>
-  <si>
-    <t>0.2134,0.0317,0.0182,0.8752</t>
-  </si>
-  <si>
-    <t>0.7246,0.0521,0.1656,0.0274</t>
-  </si>
-  <si>
-    <t>0.5966,0.0250,0.3655,0.0616</t>
-  </si>
-  <si>
-    <t>0.0925,0.0139,0.9121,0.0280</t>
-  </si>
-  <si>
-    <t>0.0289,0.1263,0.8994,0.0050</t>
-  </si>
-  <si>
-    <t>0.0085,0.2399,0.9319,0.0013</t>
-  </si>
-  <si>
-    <t>0.0987,0.1495,0.7658,0.0307</t>
-  </si>
-  <si>
-    <t>0.0360,0.2203,0.8546,0.0068</t>
-  </si>
-  <si>
-    <t>0.9922,0.0066,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9827,0.0173,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0047,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0071,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0036,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9923,0.0057,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9929,0.0011,0.0000,0.0028</t>
-  </si>
-  <si>
-    <t>0.9839,0.0163,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.0674,0.0163,0.9449,0.0139</t>
-  </si>
-  <si>
-    <t>0.2246,0.1251,0.7366,0.0037</t>
-  </si>
-  <si>
-    <t>0.8046,0.1678,0.0208,0.0241</t>
-  </si>
-  <si>
-    <t>0.0050,0.0067,0.9882,0.0029</t>
-  </si>
-  <si>
-    <t>0.0010,0.0150,0.9911,0.0033</t>
-  </si>
-  <si>
-    <t>0.0193,0.0893,0.9366,0.0012</t>
-  </si>
-  <si>
-    <t>0.0022,0.0068,0.9954,0.0005</t>
-  </si>
-  <si>
-    <t>0.1752,0.1324,0.6632,0.0298</t>
-  </si>
-  <si>
-    <t>0.0005,0.0260,0.9938,0.0017</t>
-  </si>
-  <si>
-    <t>0.0082,0.0229,0.9540,0.0332</t>
-  </si>
-  <si>
-    <t>0.0590,0.0593,0.8881,0.0324</t>
-  </si>
-  <si>
-    <t>0.4334,0.0066,0.1492,0.3820</t>
-  </si>
-  <si>
-    <t>0.5278,0.0315,0.3785,0.0802</t>
-  </si>
-  <si>
-    <t>0.7236,0.0304,0.1575,0.0452</t>
-  </si>
-  <si>
-    <t>0.9927,0.0063,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9922,0.0037,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9932,0.0040,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9683,0.0390,0.0032,0.0012</t>
-  </si>
-  <si>
-    <t>0.9897,0.0039,0.0017,0.0022</t>
-  </si>
-  <si>
-    <t>0.9946,0.0034,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9937,0.0045,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9916,0.0122,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.1748,0.1386,0.6742,0.0149</t>
-  </si>
-  <si>
-    <t>0.0016,0.0311,0.9907,0.0023</t>
-  </si>
-  <si>
-    <t>0.0149,0.0287,0.9567,0.0130</t>
-  </si>
-  <si>
-    <t>0.0552,0.0187,0.9231,0.0153</t>
-  </si>
-  <si>
-    <t>0.0078,0.0150,0.9711,0.0111</t>
-  </si>
-  <si>
-    <t>0.0708,0.0235,0.8990,0.0559</t>
-  </si>
-  <si>
-    <t>0.0688,0.0340,0.9132,0.0115</t>
-  </si>
-  <si>
-    <t>0.1079,0.0208,0.8803,0.0108</t>
-  </si>
-  <si>
-    <t>0.6423,0.0027,0.0059,0.5323</t>
-  </si>
-  <si>
-    <t>0.0202,0.0081,0.0027,0.9896</t>
-  </si>
-  <si>
-    <t>0.0210,0.0032,0.0025,0.9894</t>
-  </si>
-  <si>
-    <t>0.0017,0.0009,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0260,0.0006,0.0015,0.9900</t>
-  </si>
-  <si>
-    <t>0.5898,0.0076,0.0070,0.5481</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7791,0.1138,0.0197,0.0856</t>
+  </si>
+  <si>
+    <t>0.0030,0.0008,0.0010,0.9980</t>
+  </si>
+  <si>
+    <t>0.2624,0.0042,0.0002,0.8685</t>
+  </si>
+  <si>
+    <t>0.0634,0.0073,0.0066,0.9684</t>
+  </si>
+  <si>
+    <t>0.9955,0.0025,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0021,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9877,0.0060,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.9918,0.0114,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0049,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9917,0.0058,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0049,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0023,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.6724,0.1370,0.1563,0.0243</t>
+  </si>
+  <si>
+    <t>0.1958,0.1025,0.7530,0.0139</t>
+  </si>
+  <si>
+    <t>0.1406,0.0501,0.8586,0.0012</t>
+  </si>
+  <si>
+    <t>0.3361,0.3529,0.2399,0.0071</t>
+  </si>
+  <si>
+    <t>0.8606,0.0374,0.0756,0.0055</t>
+  </si>
+  <si>
+    <t>0.0057,0.9868,0.0060,0.0004</t>
+  </si>
+  <si>
+    <t>0.0142,0.9814,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.5137,0.5945,0.0147,0.0021</t>
+  </si>
+  <si>
+    <t>0.0405,0.9565,0.0049,0.0008</t>
+  </si>
+  <si>
+    <t>0.0026,0.9915,0.0041,0.0008</t>
+  </si>
+  <si>
+    <t>0.4638,0.0199,0.6289,0.0175</t>
+  </si>
+  <si>
+    <t>0.2989,0.0103,0.2006,0.4415</t>
+  </si>
+  <si>
+    <t>0.0162,0.0052,0.9860,0.0013</t>
+  </si>
+  <si>
+    <t>0.2895,0.0181,0.7797,0.0136</t>
+  </si>
+  <si>
+    <t>0.0220,0.0031,0.9839,0.0036</t>
+  </si>
+  <si>
+    <t>0.0368,0.0155,0.9335,0.0217</t>
+  </si>
+  <si>
+    <t>0.0018,0.0020,0.9931,0.0113</t>
+  </si>
+  <si>
+    <t>0.0261,0.9529,0.0114,0.0063</t>
+  </si>
+  <si>
+    <t>0.4573,0.2337,0.4546,0.0085</t>
+  </si>
+  <si>
+    <t>0.0196,0.0232,0.9616,0.0332</t>
+  </si>
+  <si>
+    <t>0.0031,0.9089,0.2987,0.0001</t>
+  </si>
+  <si>
+    <t>0.9252,0.0608,0.0074,0.0112</t>
+  </si>
+  <si>
+    <t>0.7369,0.1281,0.1354,0.0175</t>
+  </si>
+  <si>
+    <t>0.6806,0.3727,0.0471,0.0011</t>
+  </si>
+  <si>
+    <t>0.0261,0.8961,0.5441,0.0030</t>
+  </si>
+  <si>
+    <t>0.0172,0.7637,0.4990,0.0207</t>
+  </si>
+  <si>
+    <t>0.0478,0.1936,0.8598,0.0316</t>
+  </si>
+  <si>
+    <t>0.0431,0.1101,0.8493,0.0308</t>
+  </si>
+  <si>
+    <t>0.2232,0.0199,0.6895,0.1161</t>
+  </si>
+  <si>
+    <t>0.0050,0.5193,0.9203,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.9825,0.0461,0.0053</t>
+  </si>
+  <si>
+    <t>0.0261,0.4221,0.8098,0.0083</t>
+  </si>
+  <si>
+    <t>0.0408,0.8619,0.0099,0.3378</t>
+  </si>
+  <si>
+    <t>0.0001,0.9957,0.0019,0.0186</t>
+  </si>
+  <si>
+    <t>0.0011,0.9766,0.1554,0.0057</t>
+  </si>
+  <si>
+    <t>0.0002,0.9972,0.0160,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.1067,0.9741,0.0048</t>
+  </si>
+  <si>
+    <t>0.0064,0.1065,0.9827,0.0007</t>
+  </si>
+  <si>
+    <t>0.0419,0.0215,0.9519,0.0052</t>
+  </si>
+  <si>
+    <t>0.0106,0.0008,0.9856,0.0199</t>
+  </si>
+  <si>
+    <t>0.0017,0.0321,0.9871,0.0055</t>
+  </si>
+  <si>
+    <t>0.0098,0.1101,0.9646,0.0006</t>
+  </si>
+  <si>
+    <t>0.9646,0.0563,0.0047,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0034,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9654,0.0115,0.0091,0.0115</t>
+  </si>
+  <si>
+    <t>0.0074,0.0278,0.9846,0.0090</t>
+  </si>
+  <si>
+    <t>0.9507,0.0533,0.0083,0.0023</t>
+  </si>
+  <si>
+    <t>0.9618,0.0481,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9712,0.0254,0.0036,0.0019</t>
+  </si>
+  <si>
+    <t>0.0108,0.4414,0.9239,0.0008</t>
+  </si>
+  <si>
+    <t>0.0053,0.0281,0.9720,0.0125</t>
+  </si>
+  <si>
+    <t>0.0402,0.1129,0.8994,0.0193</t>
+  </si>
+  <si>
+    <t>0.0018,0.8673,0.9316,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0033,0.9956,0.0018</t>
+  </si>
+  <si>
+    <t>0.0553,0.8618,0.0919,0.0003</t>
+  </si>
+  <si>
+    <t>0.0058,0.9883,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.8896,0.0693,0.0439,0.0035</t>
+  </si>
+  <si>
+    <t>0.4925,0.4203,0.2019,0.0042</t>
+  </si>
+  <si>
+    <t>0.0120,0.0272,0.9639,0.0125</t>
+  </si>
+  <si>
+    <t>0.0016,0.9485,0.8069,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9473,0.8581,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9867,0.0538,0.0017</t>
+  </si>
+  <si>
+    <t>0.0021,0.9025,0.7904,0.0001</t>
+  </si>
+  <si>
+    <t>0.0063,0.0008,0.0321,0.9856</t>
+  </si>
+  <si>
+    <t>0.0037,0.0023,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0474,0.0073,0.0033,0.9795</t>
+  </si>
+  <si>
+    <t>0.0039,0.0035,0.0026,0.9964</t>
+  </si>
+  <si>
+    <t>0.0259,0.0030,0.0027,0.9895</t>
+  </si>
+  <si>
+    <t>0.0047,0.0032,0.0010,0.9970</t>
+  </si>
+  <si>
+    <t>0.0014,0.9495,0.8118,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.6969,0.9782,0.0001</t>
+  </si>
+  <si>
+    <t>0.0230,0.7326,0.4896,0.0053</t>
+  </si>
+  <si>
+    <t>0.0018,0.6340,0.9767,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.8980,0.9546,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.6699,0.6920,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0030,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9953,0.0055,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0054,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9872,0.0056,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9933,0.0039,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9908,0.0055,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9897,0.0049,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9073,0.1823,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9761,0.0033,0.0001,0.0113</t>
+  </si>
+  <si>
+    <t>0.9957,0.0008,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9933,0.0023,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0029,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9955,0.0024,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9952,0.0026,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9929,0.0019,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.0077,0.0063,0.9708,0.0410</t>
+  </si>
+  <si>
+    <t>0.0142,0.0037,0.9879,0.0029</t>
+  </si>
+  <si>
+    <t>0.2743,0.0290,0.1832,0.6094</t>
+  </si>
+  <si>
+    <t>0.0347,0.0413,0.9361,0.0017</t>
+  </si>
+  <si>
+    <t>0.0172,0.9759,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.0054,0.9884,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.0347,0.9623,0.0018,0.0028</t>
+  </si>
+  <si>
+    <t>0.0987,0.9286,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.0376,0.9527,0.0134,0.0047</t>
+  </si>
+  <si>
+    <t>0.0156,0.9782,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.2760,0.7980,0.0047,0.0006</t>
+  </si>
+  <si>
+    <t>0.5482,0.0541,0.4919,0.0113</t>
+  </si>
+  <si>
+    <t>0.5649,0.0561,0.5005,0.0065</t>
+  </si>
+  <si>
+    <t>0.5938,0.0168,0.1667,0.1453</t>
+  </si>
+  <si>
+    <t>0.5357,0.0809,0.4828,0.0141</t>
+  </si>
+  <si>
+    <t>0.1824,0.5727,0.0743,0.4774</t>
+  </si>
+  <si>
+    <t>0.0005,0.9972,0.0055,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9926,0.0139,0.0103</t>
+  </si>
+  <si>
+    <t>0.0383,0.8005,0.0510,0.3618</t>
+  </si>
+  <si>
+    <t>0.0001,0.9880,0.7570,0.0002</t>
+  </si>
+  <si>
+    <t>0.0089,0.9840,0.0679,0.0002</t>
+  </si>
+  <si>
+    <t>0.9271,0.0830,0.0198,0.0014</t>
+  </si>
+  <si>
+    <t>0.4709,0.6258,0.0266,0.0017</t>
+  </si>
+  <si>
+    <t>0.9930,0.0029,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9848,0.0064,0.0005,0.0047</t>
+  </si>
+  <si>
+    <t>0.9844,0.0076,0.0008,0.0035</t>
+  </si>
+  <si>
+    <t>0.9620,0.0352,0.0035,0.0031</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9685,0.0120,0.0023,0.0073</t>
+  </si>
+  <si>
+    <t>0.9872,0.0028,0.0004,0.0049</t>
+  </si>
+  <si>
+    <t>0.9900,0.0035,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.0011,0.5373,0.9782,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.5716,0.9138,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.6571,0.7971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0260,0.0736,0.9480,0.0014</t>
+  </si>
+  <si>
+    <t>0.5839,0.0584,0.2803,0.0862</t>
+  </si>
+  <si>
+    <t>0.6618,0.0908,0.2970,0.0220</t>
+  </si>
+  <si>
+    <t>0.1522,0.0065,0.9296,0.0120</t>
+  </si>
+  <si>
+    <t>0.3224,0.1245,0.6346,0.0505</t>
+  </si>
+  <si>
+    <t>0.0294,0.0014,0.0013,0.9904</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0142,0.0019,0.0009,0.9950</t>
+  </si>
+  <si>
+    <t>0.0145,0.0040,0.0019,0.9930</t>
+  </si>
+  <si>
+    <t>0.0026,0.8865,0.7531,0.0016</t>
+  </si>
+  <si>
+    <t>0.9466,0.0546,0.0015,0.0048</t>
+  </si>
+  <si>
+    <t>0.3205,0.6660,0.0581,0.0123</t>
+  </si>
+  <si>
+    <t>0.9774,0.0042,0.0008,0.0122</t>
+  </si>
+  <si>
+    <t>0.8997,0.1732,0.0064,0.0019</t>
+  </si>
+  <si>
+    <t>0.9255,0.0090,0.0182,0.0309</t>
+  </si>
+  <si>
+    <t>0.7845,0.0133,0.0802,0.1086</t>
+  </si>
+  <si>
+    <t>0.9493,0.0174,0.0229,0.0064</t>
+  </si>
+  <si>
+    <t>0.0005,0.1060,0.9900,0.0017</t>
+  </si>
+  <si>
+    <t>0.8805,0.0022,0.0054,0.1296</t>
+  </si>
+  <si>
+    <t>0.8980,0.0395,0.0224,0.0342</t>
+  </si>
+  <si>
+    <t>0.8044,0.1918,0.0253,0.0089</t>
+  </si>
+  <si>
+    <t>0.8942,0.0723,0.0215,0.0065</t>
+  </si>
+  <si>
+    <t>0.7290,0.3041,0.0391,0.0036</t>
+  </si>
+  <si>
+    <t>0.5740,0.3141,0.1514,0.0543</t>
+  </si>
+  <si>
+    <t>0.7978,0.1625,0.0449,0.0117</t>
+  </si>
+  <si>
+    <t>0.9113,0.1058,0.0065,0.0024</t>
+  </si>
+  <si>
+    <t>0.9913,0.0021,0.0004,0.0029</t>
+  </si>
+  <si>
+    <t>0.9720,0.0057,0.0008,0.0151</t>
+  </si>
+  <si>
+    <t>0.9945,0.0016,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9730,0.0100,0.0037,0.0067</t>
+  </si>
+  <si>
+    <t>0.9802,0.0066,0.0023,0.0048</t>
+  </si>
+  <si>
+    <t>0.9913,0.0034,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9947,0.0009,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.5099,0.5686,0.0383,0.0134</t>
+  </si>
+  <si>
+    <t>0.7690,0.3826,0.0117,0.0012</t>
+  </si>
+  <si>
+    <t>0.2859,0.7766,0.0051,0.0048</t>
+  </si>
+  <si>
+    <t>0.1278,0.2089,0.8803,0.0022</t>
+  </si>
+  <si>
+    <t>0.9859,0.0155,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9246,0.1297,0.0071,0.0012</t>
+  </si>
+  <si>
+    <t>0.9784,0.0256,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9540,0.0455,0.0059,0.0024</t>
+  </si>
+  <si>
+    <t>0.0032,0.0276,0.9931,0.0020</t>
+  </si>
+  <si>
+    <t>0.9549,0.0899,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.0062,0.9917,0.0072</t>
+  </si>
+  <si>
+    <t>0.0096,0.0294,0.9822,0.0023</t>
+  </si>
+  <si>
+    <t>0.0277,0.0283,0.9577,0.0008</t>
+  </si>
+  <si>
+    <t>0.0088,0.0721,0.9729,0.0038</t>
+  </si>
+  <si>
+    <t>0.0309,0.0089,0.9736,0.0012</t>
+  </si>
+  <si>
+    <t>0.0050,0.0022,0.9924,0.0035</t>
+  </si>
+  <si>
+    <t>0.0147,0.0036,0.9843,0.0045</t>
+  </si>
+  <si>
+    <t>0.2764,0.4286,0.4105,0.0691</t>
+  </si>
+  <si>
+    <t>0.3517,0.1409,0.5374,0.0177</t>
+  </si>
+  <si>
+    <t>0.5950,0.0365,0.3702,0.0560</t>
+  </si>
+  <si>
+    <t>0.2613,0.1154,0.6784,0.0024</t>
+  </si>
+  <si>
+    <t>0.2728,0.3530,0.4192,0.0077</t>
+  </si>
+  <si>
+    <t>0.6506,0.0619,0.2652,0.0311</t>
+  </si>
+  <si>
+    <t>0.6746,0.0686,0.1703,0.0760</t>
+  </si>
+  <si>
+    <t>0.2963,0.0569,0.7766,0.0032</t>
+  </si>
+  <si>
+    <t>0.7895,0.4002,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.5489,0.6846,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.8573,0.2314,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.9492,0.0955,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9731,0.0361,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.6443,0.0555,0.2257,0.0688</t>
+  </si>
+  <si>
+    <t>0.5563,0.0429,0.4506,0.0412</t>
+  </si>
+  <si>
+    <t>0.8065,0.0207,0.0902,0.0246</t>
+  </si>
+  <si>
+    <t>0.3715,0.0889,0.5036,0.1350</t>
+  </si>
+  <si>
+    <t>0.6563,0.0190,0.1284,0.1459</t>
+  </si>
+  <si>
+    <t>0.0040,0.0054,0.9645,0.2236</t>
+  </si>
+  <si>
+    <t>0.0082,0.1515,0.9125,0.0184</t>
+  </si>
+  <si>
+    <t>0.0305,0.0494,0.9053,0.0311</t>
+  </si>
+  <si>
+    <t>0.0709,0.1739,0.8141,0.0043</t>
+  </si>
+  <si>
+    <t>0.0115,0.0460,0.9568,0.0035</t>
+  </si>
+  <si>
+    <t>0.9925,0.0055,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9882,0.0047,0.0003,0.0025</t>
+  </si>
+  <si>
+    <t>0.9918,0.0064,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0091,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9953,0.0021,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0022,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9939,0.0020,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9901,0.0043,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.0161,0.0158,0.9846,0.0009</t>
+  </si>
+  <si>
+    <t>0.2479,0.0461,0.8636,0.0048</t>
+  </si>
+  <si>
+    <t>0.6340,0.0711,0.1498,0.1749</t>
+  </si>
+  <si>
+    <t>0.0097,0.0394,0.9681,0.0015</t>
+  </si>
+  <si>
+    <t>0.0067,0.0289,0.9774,0.0047</t>
+  </si>
+  <si>
+    <t>0.0218,0.0455,0.9339,0.0174</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9969,0.0067</t>
+  </si>
+  <si>
+    <t>0.0573,0.0083,0.9533,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0253,0.9920,0.0021</t>
+  </si>
+  <si>
+    <t>0.0911,0.0273,0.9147,0.0133</t>
+  </si>
+  <si>
+    <t>0.1422,0.2763,0.6387,0.0344</t>
+  </si>
+  <si>
+    <t>0.4934,0.0363,0.4271,0.1206</t>
+  </si>
+  <si>
+    <t>0.6121,0.0030,0.5447,0.0131</t>
+  </si>
+  <si>
+    <t>0.4880,0.0377,0.0178,0.5070</t>
+  </si>
+  <si>
+    <t>0.9933,0.0042,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9939,0.0080,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0036,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9943,0.0022,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9931,0.0013,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9935,0.0062,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0018,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9882,0.0089,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0111,0.2922,0.9209,0.0031</t>
+  </si>
+  <si>
+    <t>0.0032,0.0886,0.9796,0.0050</t>
+  </si>
+  <si>
+    <t>0.0054,0.0268,0.9711,0.0166</t>
+  </si>
+  <si>
+    <t>0.1153,0.1472,0.7541,0.0200</t>
+  </si>
+  <si>
+    <t>0.0054,0.0046,0.9861,0.0111</t>
+  </si>
+  <si>
+    <t>0.1333,0.0359,0.8056,0.1048</t>
+  </si>
+  <si>
+    <t>0.0544,0.1350,0.8910,0.0184</t>
+  </si>
+  <si>
+    <t>0.0173,0.0310,0.9386,0.0325</t>
+  </si>
+  <si>
+    <t>0.6653,0.0028,0.0075,0.4895</t>
+  </si>
+  <si>
+    <t>0.0491,0.0319,0.0004,0.9676</t>
+  </si>
+  <si>
+    <t>0.0180,0.0009,0.0008,0.9935</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.0059,0.9970</t>
+  </si>
+  <si>
+    <t>0.0046,0.0003,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.4672,0.0618,0.0093,0.5035</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2172,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2466,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2536,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2581,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2816,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3572,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5210,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
